--- a/annotators/team/tg/annotated/ted-mdb.2150.xlsx
+++ b/annotators/team/tg/annotated/ted-mdb.2150.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\in-progress\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\annotated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2635ADE2-2356-49AD-B0D1-B37434ECB933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AC416E-BD6E-45E4-99CE-2B44199ADD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2258" uniqueCount="607">
   <si>
     <t>ID</t>
   </si>
@@ -1631,15 +1631,9 @@
     <t>visionen</t>
   </si>
   <si>
-    <t>CHECK: Städte oder Karten?</t>
-  </si>
-  <si>
     <t>beziehungen_menschen</t>
   </si>
   <si>
-    <t>CHECK ob ID</t>
-  </si>
-  <si>
     <t>Antezedens</t>
   </si>
   <si>
@@ -1721,9 +1715,6 @@
     <t>karte_baltimore</t>
   </si>
   <si>
-    <t>gruppierungen</t>
-  </si>
-  <si>
     <t>karte_baltimore_gruen</t>
   </si>
   <si>
@@ -1763,9 +1754,6 @@
     <t>später referenziert</t>
   </si>
   <si>
-    <t>CHECK: Stadt oder Karte?</t>
-  </si>
-  <si>
     <t>syntaktischer Kopf</t>
   </si>
   <si>
@@ -1851,6 +1839,9 @@
   </si>
   <si>
     <t>vielfalt_stadtentwicklung</t>
+  </si>
+  <si>
+    <t>Stadt oder Karte?; siehe log</t>
   </si>
 </sst>
 </file>
@@ -2642,7 +2633,7 @@
         <v>53</v>
       </c>
       <c r="E4" s="21" t="str">
-        <f t="shared" ref="E3:E13" si="1">IF(D4="?OLD","!!!","")</f>
+        <f t="shared" ref="E4:E13" si="1">IF(D4="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F4" s="22" t="str">
@@ -3255,7 +3246,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="L22" s="26" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
@@ -3963,7 +3954,7 @@
         <v/>
       </c>
       <c r="L41" s="26" t="s">
-        <v>580</v>
+        <v>606</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -4182,7 +4173,7 @@
         <v>70</v>
       </c>
       <c r="E48" s="21" t="str">
-        <f t="shared" ref="E48:E79" si="4">IF(D48="?OLD","!!!","")</f>
+        <f t="shared" ref="E48:E78" si="4">IF(D48="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F48" s="22" t="str">
@@ -4569,7 +4560,7 @@
         <v/>
       </c>
       <c r="L58" s="26" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
@@ -4933,7 +4924,7 @@
         <v/>
       </c>
       <c r="L68" s="26" t="s">
-        <v>536</v>
+        <v>606</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
@@ -5311,7 +5302,7 @@
         <v>52</v>
       </c>
       <c r="E79" s="21" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="F79" s="22" t="s">
         <v>509</v>
@@ -5343,7 +5334,7 @@
         <v>125</v>
       </c>
       <c r="E80" s="21" t="str">
-        <f t="shared" ref="E80:E111" si="6">IF(D80="?OLD","!!!","")</f>
+        <f t="shared" ref="E80:E103" si="6">IF(D80="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F80" s="22" t="str">
@@ -5355,7 +5346,7 @@
         <v/>
       </c>
       <c r="H80" s="24" t="str">
-        <f t="shared" ref="H80:H111" ca="1" si="7">IF(J80&lt;&gt;1,"",IF(I80="SBJ","CB","?"))</f>
+        <f t="shared" ref="H80:H103" ca="1" si="7">IF(J80&lt;&gt;1,"",IF(I80="SBJ","CB","?"))</f>
         <v/>
       </c>
       <c r="I80" s="25" t="str">
@@ -5411,7 +5402,7 @@
         <v>104</v>
       </c>
       <c r="E82" s="21" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F82" s="22" t="s">
         <v>513</v>
@@ -5630,7 +5621,7 @@
         <v>52</v>
       </c>
       <c r="E88" s="21" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F88" s="22" t="str">
         <f>IF(OR(E88="",E88="!!!"),"",IF(NOT(ISNA(VLOOKUP(E88,E$1:E87,1,FALSE()))),"OLD",IF(AND(E88&lt;&gt;"",E88&lt;&gt;"!!!"),"NEW","")))</f>
@@ -5808,7 +5799,7 @@
         <v>52</v>
       </c>
       <c r="E93" s="21" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F93" s="22" t="str">
         <f>IF(OR(E93="",E93="!!!"),"",IF(NOT(ISNA(VLOOKUP(E93,E$1:E92,1,FALSE()))),"OLD",IF(AND(E93&lt;&gt;"",E93&lt;&gt;"!!!"),"NEW","")))</f>
@@ -6259,7 +6250,7 @@
         <v>142</v>
       </c>
       <c r="E107" s="21" t="str">
-        <f t="shared" ref="E106:E169" si="9">IF(D107="?OLD","!!!","")</f>
+        <f t="shared" ref="E107:E169" si="9">IF(D107="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F107" s="22" t="str">
@@ -7045,35 +7036,31 @@
       <c r="D128" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E128" s="21" t="s">
-        <v>566</v>
-      </c>
+      <c r="E128" s="21"/>
       <c r="F128" s="22" t="s">
         <v>509</v>
       </c>
-      <c r="G128" s="23" t="e">
-        <f ca="1">IF(OR(E128="",E128="!!!"),"",IF(OR(J128=0,AND(J128=1,K128=1),AND(J128=1,I128="SBJ"),AND(J128=1,I128=0)),"?IN_FOCUS",IF(J128&lt;=2,"?ACTIVATED",IF(J128&lt;&gt;"","?FAMILIAR",IF(F128="NEW",IF(ISNA(VLOOKUP(E128,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v>#VALUE!</v>
+      <c r="G128" s="23" t="str">
+        <f>IF(OR(E128="",E128="!!!"),"",IF(OR(J128=0,AND(J128=1,K128=1),AND(J128=1,I128="SBJ"),AND(J128=1,I128=0)),"?IN_FOCUS",IF(J128&lt;=2,"?ACTIVATED",IF(J128&lt;&gt;"","?FAMILIAR",IF(F128="NEW",IF(ISNA(VLOOKUP(E128,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v/>
       </c>
       <c r="H128" s="24" t="str">
         <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
-      <c r="I128" s="25" t="e">
+      <c r="I128" s="25" t="str">
         <f>IF(OR(E128="",E128="!!!",F128="NEW"),"",INDEX(B$2:B127,-1+SUMPRODUCT(MAX(ROW(E$2:E127)*(E128=E$2:E127)))))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J128" s="25">
+        <v/>
+      </c>
+      <c r="J128" s="25" t="str">
         <f ca="1">IF(OR(E128="",E128="!!!",F128="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E128)*(E128=E$2:E128)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E127)*(E2=E$1:E127))))))</f>
-        <v>0</v>
-      </c>
-      <c r="K128" s="25" t="e">
+        <v/>
+      </c>
+      <c r="K128" s="25" t="str">
         <f>IF(OR(E128="",E128="!!!",F128="NEW"),"",INDEX(J$1:J127,SUMPRODUCT(MAX(ROW(E$1:E127)*(E128=E$1:E127)))))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L128" s="26" t="s">
-        <v>538</v>
-      </c>
+        <v/>
+      </c>
+      <c r="L128" s="26"/>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
@@ -7165,7 +7152,7 @@
         <v>52</v>
       </c>
       <c r="E131" s="21" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F131" s="22" t="str">
         <f>IF(OR(E131="",E131="!!!"),"",IF(NOT(ISNA(VLOOKUP(E131,E$1:E130,1,FALSE()))),"OLD",IF(AND(E131&lt;&gt;"",E131&lt;&gt;"!!!"),"NEW","")))</f>
@@ -7453,7 +7440,7 @@
         <v>52</v>
       </c>
       <c r="E139" s="21" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="F139" s="22" t="s">
         <v>513</v>
@@ -7732,7 +7719,7 @@
         <v>52</v>
       </c>
       <c r="E147" s="21" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F147" s="22" t="s">
         <v>513</v>
@@ -7875,7 +7862,7 @@
         <v>52</v>
       </c>
       <c r="E151" s="21" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F151" s="22" t="str">
         <f>IF(OR(E151="",E151="!!!"),"",IF(NOT(ISNA(VLOOKUP(E151,E$1:E150,1,FALSE()))),"OLD",IF(AND(E151&lt;&gt;"",E151&lt;&gt;"!!!"),"NEW","")))</f>
@@ -8472,7 +8459,7 @@
         <v>52</v>
       </c>
       <c r="E168" s="21" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="F168" s="22" t="s">
         <v>513</v>
@@ -8547,7 +8534,7 @@
         <v>52</v>
       </c>
       <c r="E170" s="21" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F170" s="22" t="str">
         <f>IF(OR(E170="",E170="!!!"),"",IF(NOT(ISNA(VLOOKUP(E170,E$1:E169,1,FALSE()))),"OLD",IF(AND(E170&lt;&gt;"",E170&lt;&gt;"!!!"),"NEW","")))</f>
@@ -8580,7 +8567,7 @@
         <v>105</v>
       </c>
       <c r="E171" s="21" t="str">
-        <f t="shared" ref="E170:E233" si="11">IF(D171="?OLD","!!!","")</f>
+        <f t="shared" ref="E171:E233" si="11">IF(D171="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F171" s="22" t="str">
@@ -8688,7 +8675,7 @@
         <v>58</v>
       </c>
       <c r="E174" s="21" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="F174" s="22" t="str">
         <f>IF(OR(E174="",E174="!!!"),"",IF(NOT(ISNA(VLOOKUP(E174,E$1:E173,1,FALSE()))),"OLD",IF(AND(E174&lt;&gt;"",E174&lt;&gt;"!!!"),"NEW","")))</f>
@@ -9153,7 +9140,7 @@
         <v>52</v>
       </c>
       <c r="E187" s="21" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F187" s="22" t="str">
         <f>IF(OR(E187="",E187="!!!"),"",IF(NOT(ISNA(VLOOKUP(E187,E$1:E186,1,FALSE()))),"OLD",IF(AND(E187&lt;&gt;"",E187&lt;&gt;"!!!"),"NEW","")))</f>
@@ -9549,7 +9536,7 @@
         <v>52</v>
       </c>
       <c r="E198" s="21" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="F198" s="22" t="str">
         <f>IF(OR(E198="",E198="!!!"),"",IF(NOT(ISNA(VLOOKUP(E198,E$1:E197,1,FALSE()))),"OLD",IF(AND(E198&lt;&gt;"",E198&lt;&gt;"!!!"),"NEW","")))</f>
@@ -9625,7 +9612,7 @@
         <v>52</v>
       </c>
       <c r="E200" s="21" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F200" s="22" t="str">
         <f>IF(OR(E200="",E200="!!!"),"",IF(NOT(ISNA(VLOOKUP(E200,E$1:E199,1,FALSE()))),"OLD",IF(AND(E200&lt;&gt;"",E200&lt;&gt;"!!!"),"NEW","")))</f>
@@ -9924,7 +9911,7 @@
         <v>52</v>
       </c>
       <c r="E208" s="21" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F208" s="22" t="s">
         <v>523</v>
@@ -10384,7 +10371,7 @@
         <v>52</v>
       </c>
       <c r="E221" s="21" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F221" s="22" t="s">
         <v>523</v>
@@ -10595,7 +10582,7 @@
         <v>52</v>
       </c>
       <c r="E227" s="21" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F227" s="22" t="s">
         <v>523</v>
@@ -10704,7 +10691,7 @@
         <v>52</v>
       </c>
       <c r="E230" s="21" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F230" s="22" t="s">
         <v>523</v>
@@ -10847,7 +10834,7 @@
         <v>52</v>
       </c>
       <c r="E234" s="21" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F234" s="22" t="str">
         <f>IF(OR(E234="",E234="!!!"),"",IF(NOT(ISNA(VLOOKUP(E234,E$1:E233,1,FALSE()))),"OLD",IF(AND(E234&lt;&gt;"",E234&lt;&gt;"!!!"),"NEW","")))</f>
@@ -10880,7 +10867,7 @@
         <v>59</v>
       </c>
       <c r="E235" s="21" t="str">
-        <f t="shared" ref="E234:E297" si="13">IF(D235="?OLD","!!!","")</f>
+        <f t="shared" ref="E235:E296" si="13">IF(D235="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F235" s="22" t="str">
@@ -11209,7 +11196,7 @@
         <v>52</v>
       </c>
       <c r="E244" s="21" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="F244" s="22" t="s">
         <v>513</v>
@@ -11284,7 +11271,7 @@
         <v>52</v>
       </c>
       <c r="E246" s="21" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F246" s="22" t="str">
         <f>IF(OR(E246="",E246="!!!"),"",IF(NOT(ISNA(VLOOKUP(E246,E$1:E245,1,FALSE()))),"OLD",IF(AND(E246&lt;&gt;"",E246&lt;&gt;"!!!"),"NEW","")))</f>
@@ -11396,7 +11383,7 @@
         <v>58</v>
       </c>
       <c r="E249" s="21" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="F249" s="22" t="str">
         <f>IF(OR(E249="",E249="!!!"),"",IF(NOT(ISNA(VLOOKUP(E249,E$1:E248,1,FALSE()))),"OLD",IF(AND(E249&lt;&gt;"",E249&lt;&gt;"!!!"),"NEW","")))</f>
@@ -11423,7 +11410,7 @@
         <v/>
       </c>
       <c r="L249" s="26" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.3">
@@ -12007,7 +11994,7 @@
         <v>52</v>
       </c>
       <c r="E266" s="21" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F266" s="22" t="s">
         <v>516</v>
@@ -12158,7 +12145,7 @@
         <v>52</v>
       </c>
       <c r="E270" s="21" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F270" s="22" t="str">
         <f>IF(OR(E270="",E270="!!!"),"",IF(NOT(ISNA(VLOOKUP(E270,E$1:E269,1,FALSE()))),"OLD",IF(AND(E270&lt;&gt;"",E270&lt;&gt;"!!!"),"NEW","")))</f>
@@ -12404,7 +12391,7 @@
         <v>52</v>
       </c>
       <c r="E277" s="21" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F277" s="22" t="str">
         <f>IF(OR(E277="",E277="!!!"),"",IF(NOT(ISNA(VLOOKUP(E277,E$1:E276,1,FALSE()))),"OLD",IF(AND(E277&lt;&gt;"",E277&lt;&gt;"!!!"),"NEW","")))</f>
@@ -12624,7 +12611,7 @@
         <v>52</v>
       </c>
       <c r="E283" s="21" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="F283" s="22" t="s">
         <v>513</v>
@@ -12913,7 +12900,7 @@
         <v>52</v>
       </c>
       <c r="E291" s="21" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="F291" s="22" t="s">
         <v>522</v>
@@ -13565,7 +13552,7 @@
         <v>52</v>
       </c>
       <c r="E309" s="21" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="F309" s="22" t="s">
         <v>516</v>
@@ -13713,7 +13700,7 @@
         <v>52</v>
       </c>
       <c r="E313" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F313" s="22" t="str">
         <f>IF(OR(E313="",E313="!!!"),"",IF(NOT(ISNA(VLOOKUP(E313,E$1:E312,1,FALSE()))),"OLD",IF(AND(E313&lt;&gt;"",E313&lt;&gt;"!!!"),"NEW","")))</f>
@@ -13899,7 +13886,7 @@
         <v>52</v>
       </c>
       <c r="E318" s="21" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F318" s="22" t="s">
         <v>516</v>
@@ -14067,7 +14054,7 @@
         <v/>
       </c>
       <c r="L322" s="26" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.3">
@@ -14556,7 +14543,7 @@
         <v>52</v>
       </c>
       <c r="E336" s="21" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="F336" s="22" t="s">
         <v>522</v>
@@ -14631,7 +14618,7 @@
         <v>52</v>
       </c>
       <c r="E338" s="21" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F338" s="22" t="str">
         <f>IF(OR(E338="",E338="!!!"),"",IF(NOT(ISNA(VLOOKUP(E338,E$1:E337,1,FALSE()))),"OLD",IF(AND(E338&lt;&gt;"",E338&lt;&gt;"!!!"),"NEW","")))</f>
@@ -15106,7 +15093,7 @@
         <v>275</v>
       </c>
       <c r="E351" s="21" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="F351" s="22" t="s">
         <v>513</v>
@@ -15132,7 +15119,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="L351" s="26" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.3">
@@ -15387,7 +15374,7 @@
         <v>52</v>
       </c>
       <c r="E359" s="21" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="F359" s="22" t="s">
         <v>513</v>
@@ -15555,7 +15542,7 @@
         <v/>
       </c>
       <c r="L363" s="26" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.3">
@@ -15745,7 +15732,7 @@
         <v>58</v>
       </c>
       <c r="E369" s="21" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="F369" s="22" t="str">
         <f>IF(OR(E369="",E369="!!!"),"",IF(NOT(ISNA(VLOOKUP(E369,E$1:E368,1,FALSE()))),"OLD",IF(AND(E369&lt;&gt;"",E369&lt;&gt;"!!!"),"NEW","")))</f>
@@ -16062,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="L377" s="26" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.3">
@@ -16393,7 +16380,7 @@
         <v>52</v>
       </c>
       <c r="E387" s="21" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F387" s="22" t="s">
         <v>522</v>
@@ -16468,7 +16455,7 @@
         <v>52</v>
       </c>
       <c r="E389" s="21" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="F389" s="22" t="str">
         <f>IF(OR(E389="",E389="!!!"),"",IF(NOT(ISNA(VLOOKUP(E389,E$1:E388,1,FALSE()))),"OLD",IF(AND(E389&lt;&gt;"",E389&lt;&gt;"!!!"),"NEW","")))</f>
@@ -16541,7 +16528,7 @@
         <v>58</v>
       </c>
       <c r="E391" s="21" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="F391" s="22" t="str">
         <f>IF(OR(E391="",E391="!!!"),"",IF(NOT(ISNA(VLOOKUP(E391,E$1:E390,1,FALSE()))),"OLD",IF(AND(E391&lt;&gt;"",E391&lt;&gt;"!!!"),"NEW","")))</f>
@@ -16611,7 +16598,7 @@
         <v>173</v>
       </c>
       <c r="E393" s="21" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="F393" s="22" t="s">
         <v>523</v>
@@ -16720,7 +16707,7 @@
         <v>52</v>
       </c>
       <c r="E396" s="21" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="F396" s="22" t="s">
         <v>513</v>
@@ -16795,7 +16782,7 @@
         <v>52</v>
       </c>
       <c r="E398" s="21" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="F398" s="22" t="str">
         <f>IF(OR(E398="",E398="!!!"),"",IF(NOT(ISNA(VLOOKUP(E398,E$1:E397,1,FALSE()))),"OLD",IF(AND(E398&lt;&gt;"",E398&lt;&gt;"!!!"),"NEW","")))</f>
@@ -16970,7 +16957,7 @@
         <v>102</v>
       </c>
       <c r="E403" s="21" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="F403" s="22" t="str">
         <f>IF(OR(E403="",E403="!!!"),"",IF(NOT(ISNA(VLOOKUP(E403,E$1:E402,1,FALSE()))),"OLD",IF(AND(E403&lt;&gt;"",E403&lt;&gt;"!!!"),"NEW","")))</f>
@@ -16997,7 +16984,7 @@
         <v/>
       </c>
       <c r="L403" s="26" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="404" spans="1:12" x14ac:dyDescent="0.3">
@@ -17073,7 +17060,7 @@
         <v/>
       </c>
       <c r="L405" s="26" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="406" spans="1:12" x14ac:dyDescent="0.3">
@@ -17367,7 +17354,7 @@
         <v>52</v>
       </c>
       <c r="E414" s="21" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="F414" s="22" t="str">
         <f>IF(OR(E414="",E414="!!!"),"",IF(NOT(ISNA(VLOOKUP(E414,E$1:E413,1,FALSE()))),"OLD",IF(AND(E414&lt;&gt;"",E414&lt;&gt;"!!!"),"NEW","")))</f>
@@ -17721,7 +17708,7 @@
         <v>52</v>
       </c>
       <c r="E424" s="21" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="F424" s="22" t="str">
         <f>IF(OR(E424="",E424="!!!"),"",IF(NOT(ISNA(VLOOKUP(E424,E$1:E423,1,FALSE()))),"OLD",IF(AND(E424&lt;&gt;"",E424&lt;&gt;"!!!"),"NEW","")))</f>
@@ -17788,7 +17775,7 @@
         <v>133</v>
       </c>
       <c r="E426" s="21" t="str">
-        <f t="shared" ref="E426:E489" si="18">IF(D426="?OLD","!!!","")</f>
+        <f t="shared" ref="E426:E488" si="18">IF(D426="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F426" s="22" t="str">
@@ -18081,7 +18068,7 @@
         <v>52</v>
       </c>
       <c r="E434" s="21" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="F434" s="22" t="s">
         <v>513</v>
@@ -18292,7 +18279,7 @@
         <v>52</v>
       </c>
       <c r="E440" s="21" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="F440" s="22" t="str">
         <f>IF(OR(E440="",E440="!!!"),"",IF(NOT(ISNA(VLOOKUP(E440,E$1:E439,1,FALSE()))),"OLD",IF(AND(E440&lt;&gt;"",E440&lt;&gt;"!!!"),"NEW","")))</f>
@@ -18580,7 +18567,7 @@
         <v>52</v>
       </c>
       <c r="E448" s="21" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="F448" s="22" t="str">
         <f>IF(OR(E448="",E448="!!!"),"",IF(NOT(ISNA(VLOOKUP(E448,E$1:E447,1,FALSE()))),"OLD",IF(AND(E448&lt;&gt;"",E448&lt;&gt;"!!!"),"NEW","")))</f>
@@ -19017,7 +19004,7 @@
         <v>52</v>
       </c>
       <c r="E460" s="21" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="F460" s="22" t="str">
         <f>IF(OR(E460="",E460="!!!"),"",IF(NOT(ISNA(VLOOKUP(E460,E$1:E459,1,FALSE()))),"OLD",IF(AND(E460&lt;&gt;"",E460&lt;&gt;"!!!"),"NEW","")))</f>
@@ -19379,7 +19366,7 @@
         <v>52</v>
       </c>
       <c r="E470" s="21" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="F470" s="22" t="str">
         <f>IF(OR(E470="",E470="!!!"),"",IF(NOT(ISNA(VLOOKUP(E470,E$1:E469,1,FALSE()))),"OLD",IF(AND(E470&lt;&gt;"",E470&lt;&gt;"!!!"),"NEW","")))</f>
@@ -20052,7 +20039,7 @@
         <v>162</v>
       </c>
       <c r="E489" s="21" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="F489" s="22" t="str">
         <f>IF(OR(E489="",E489="!!!"),"",IF(NOT(ISNA(VLOOKUP(E489,E$1:E488,1,FALSE()))),"OLD",IF(AND(E489&lt;&gt;"",E489&lt;&gt;"!!!"),"NEW","")))</f>
@@ -20079,7 +20066,7 @@
         <v>0</v>
       </c>
       <c r="L489" s="26" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="490" spans="1:12" x14ac:dyDescent="0.3">
@@ -20087,7 +20074,7 @@
         <v>318</v>
       </c>
       <c r="E490" s="21" t="str">
-        <f t="shared" ref="E490:E553" si="20">IF(D490="?OLD","!!!","")</f>
+        <f t="shared" ref="E490:E508" si="20">IF(D490="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F490" s="22" t="str">
@@ -20099,7 +20086,7 @@
         <v/>
       </c>
       <c r="H490" s="24" t="str">
-        <f t="shared" ref="H490:H553" ca="1" si="21">IF(J490&lt;&gt;1,"",IF(I490="SBJ","CB","?"))</f>
+        <f t="shared" ref="H490:H508" ca="1" si="21">IF(J490&lt;&gt;1,"",IF(I490="SBJ","CB","?"))</f>
         <v/>
       </c>
       <c r="I490" s="25" t="str">
@@ -20274,7 +20261,7 @@
         <v>52</v>
       </c>
       <c r="E495" s="21" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="F495" s="22" t="str">
         <f>IF(OR(E495="",E495="!!!"),"",IF(NOT(ISNA(VLOOKUP(E495,E$1:E494,1,FALSE()))),"OLD",IF(AND(E495&lt;&gt;"",E495&lt;&gt;"!!!"),"NEW","")))</f>
@@ -20557,7 +20544,7 @@
         <v>52</v>
       </c>
       <c r="E503" s="21" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="F503" s="22" t="str">
         <f>IF(OR(E503="",E503="!!!"),"",IF(NOT(ISNA(VLOOKUP(E503,E$1:E502,1,FALSE()))),"OLD",IF(AND(E503&lt;&gt;"",E503&lt;&gt;"!!!"),"NEW","")))</f>
@@ -20701,7 +20688,7 @@
         <v>52</v>
       </c>
       <c r="E507" s="21" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="F507" s="22" t="str">
         <f>IF(OR(E507="",E507="!!!"),"",IF(NOT(ISNA(VLOOKUP(E507,E$1:E506,1,FALSE()))),"OLD",IF(AND(E507&lt;&gt;"",E507&lt;&gt;"!!!"),"NEW","")))</f>
@@ -20850,7 +20837,7 @@
         <v>52</v>
       </c>
       <c r="E513" s="21" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="F513" s="22" t="str">
         <f>IF(OR(E513="",E513="!!!"),"",IF(NOT(ISNA(VLOOKUP(E513,E$1:E512,1,FALSE()))),"OLD",IF(AND(E513&lt;&gt;"",E513&lt;&gt;"!!!"),"NEW","")))</f>
@@ -20960,7 +20947,7 @@
         <v>52</v>
       </c>
       <c r="E516" s="21" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="F516" s="22" t="str">
         <f>IF(OR(E516="",E516="!!!"),"",IF(NOT(ISNA(VLOOKUP(E516,E$1:E515,1,FALSE()))),"OLD",IF(AND(E516&lt;&gt;"",E516&lt;&gt;"!!!"),"NEW","")))</f>
@@ -21150,7 +21137,7 @@
         <v>52</v>
       </c>
       <c r="E521" s="21" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="F521" s="22" t="s">
         <v>513</v>
@@ -21468,7 +21455,7 @@
         <v>52</v>
       </c>
       <c r="E530" s="21" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="F530" s="22" t="s">
         <v>523</v>
@@ -21733,7 +21720,7 @@
         <v>52</v>
       </c>
       <c r="E537" s="21" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="F537" s="22" t="str">
         <f>IF(OR(E537="",E537="!!!"),"",IF(NOT(ISNA(VLOOKUP(E537,E$1:E536,1,FALSE()))),"OLD",IF(AND(E537&lt;&gt;"",E537&lt;&gt;"!!!"),"NEW","")))</f>
@@ -21877,7 +21864,7 @@
         <v>52</v>
       </c>
       <c r="E541" s="21" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="F541" s="22" t="str">
         <f>IF(OR(E541="",E541="!!!"),"",IF(NOT(ISNA(VLOOKUP(E541,E$1:E540,1,FALSE()))),"OLD",IF(AND(E541&lt;&gt;"",E541&lt;&gt;"!!!"),"NEW","")))</f>
@@ -21987,7 +21974,7 @@
         <v>52</v>
       </c>
       <c r="E544" s="21" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="F544" s="22" t="str">
         <f>IF(OR(E544="",E544="!!!"),"",IF(NOT(ISNA(VLOOKUP(E544,E$1:E543,1,FALSE()))),"OLD",IF(AND(E544&lt;&gt;"",E544&lt;&gt;"!!!"),"NEW","")))</f>
@@ -22014,7 +22001,7 @@
         <v/>
       </c>
       <c r="L544" s="26" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="545" spans="1:12" x14ac:dyDescent="0.3">
@@ -22683,7 +22670,7 @@
         <v>90</v>
       </c>
       <c r="E563" s="21" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="F563" s="22" t="str">
         <f>IF(OR(E563="",E563="!!!"),"",IF(NOT(ISNA(VLOOKUP(E563,E$1:E562,1,FALSE()))),"OLD",IF(AND(E563&lt;&gt;"",E563&lt;&gt;"!!!"),"NEW","")))</f>
@@ -23201,7 +23188,7 @@
         <v>58</v>
       </c>
       <c r="E577" s="21" t="str">
-        <f t="shared" ref="E576:E639" si="25">IF(D577="?OLD","!!!","")</f>
+        <f t="shared" ref="E577:E639" si="25">IF(D577="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F577" s="22" t="str">
@@ -23385,7 +23372,7 @@
         <v>102</v>
       </c>
       <c r="E582" s="21" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="F582" s="22" t="str">
         <f>IF(OR(E582="",E582="!!!"),"",IF(NOT(ISNA(VLOOKUP(E582,E$1:E581,1,FALSE()))),"OLD",IF(AND(E582&lt;&gt;"",E582&lt;&gt;"!!!"),"NEW","")))</f>
@@ -23412,7 +23399,7 @@
         <v/>
       </c>
       <c r="L582" s="26" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="583" spans="1:12" x14ac:dyDescent="0.3">
@@ -24588,7 +24575,7 @@
         <v>52</v>
       </c>
       <c r="E615" s="21" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="F615" s="22" t="str">
         <f>IF(OR(E615="",E615="!!!"),"",IF(NOT(ISNA(VLOOKUP(E615,E$1:E614,1,FALSE()))),"OLD",IF(AND(E615&lt;&gt;"",E615&lt;&gt;"!!!"),"NEW","")))</f>
@@ -25645,7 +25632,7 @@
         <v>52</v>
       </c>
       <c r="E644" s="21" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F644" s="22" t="str">
         <f>IF(OR(E644="",E644="!!!"),"",IF(NOT(ISNA(VLOOKUP(E644,E$1:E643,1,FALSE()))),"OLD",IF(AND(E644&lt;&gt;"",E644&lt;&gt;"!!!"),"NEW","")))</f>
@@ -26284,7 +26271,7 @@
         <v>52</v>
       </c>
       <c r="E662" s="21" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="F662" s="22" t="str">
         <f>IF(OR(E662="",E662="!!!"),"",IF(NOT(ISNA(VLOOKUP(E662,E$1:E661,1,FALSE()))),"OLD",IF(AND(E662&lt;&gt;"",E662&lt;&gt;"!!!"),"NEW","")))</f>
@@ -26764,7 +26751,7 @@
         <v>52</v>
       </c>
       <c r="E675" s="21" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="F675" s="22" t="str">
         <f>IF(OR(E675="",E675="!!!"),"",IF(NOT(ISNA(VLOOKUP(E675,E$1:E674,1,FALSE()))),"OLD",IF(AND(E675&lt;&gt;"",E675&lt;&gt;"!!!"),"NEW","")))</f>
@@ -27041,7 +27028,7 @@
         <v>102</v>
       </c>
       <c r="E683" s="21" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="F683" s="22" t="str">
         <f>IF(OR(E683="",E683="!!!"),"",IF(NOT(ISNA(VLOOKUP(E683,E$1:E682,1,FALSE()))),"OLD",IF(AND(E683&lt;&gt;"",E683&lt;&gt;"!!!"),"NEW","")))</f>
@@ -27779,7 +27766,7 @@
         <v>103</v>
       </c>
       <c r="E704" s="21" t="str">
-        <f t="shared" ref="E704:E767" si="28">IF(D704="?OLD","!!!","")</f>
+        <f t="shared" ref="E704:E766" si="28">IF(D704="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F704" s="22" t="str">
@@ -27937,7 +27924,7 @@
         <v>52</v>
       </c>
       <c r="E708" s="21" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F708" s="22" t="str">
         <f>IF(OR(E708="",E708="!!!"),"",IF(NOT(ISNA(VLOOKUP(E708,E$1:E707,1,FALSE()))),"OLD",IF(AND(E708&lt;&gt;"",E708&lt;&gt;"!!!"),"NEW","")))</f>
@@ -28839,7 +28826,7 @@
         <v>52</v>
       </c>
       <c r="E733" s="21" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="F733" s="22" t="str">
         <f>IF(OR(E733="",E733="!!!"),"",IF(NOT(ISNA(VLOOKUP(E733,E$1:E732,1,FALSE()))),"OLD",IF(AND(E733&lt;&gt;"",E733&lt;&gt;"!!!"),"NEW","")))</f>
@@ -29638,7 +29625,7 @@
         <v>52</v>
       </c>
       <c r="E755" s="21" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="F755" s="22" t="str">
         <f>IF(OR(E755="",E755="!!!"),"",IF(NOT(ISNA(VLOOKUP(E755,E$1:E754,1,FALSE()))),"OLD",IF(AND(E755&lt;&gt;"",E755&lt;&gt;"!!!"),"NEW","")))</f>
@@ -30151,7 +30138,7 @@
         <v>88</v>
       </c>
       <c r="E769" s="21" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="F769" s="22" t="str">
         <f>IF(OR(E769="",E769="!!!"),"",IF(NOT(ISNA(VLOOKUP(E769,E$1:E768,1,FALSE()))),"OLD",IF(AND(E769&lt;&gt;"",E769&lt;&gt;"!!!"),"NEW","")))</f>
@@ -30178,7 +30165,7 @@
         <v/>
       </c>
       <c r="L769" s="26" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="770" spans="1:12" x14ac:dyDescent="0.3">
@@ -30254,7 +30241,7 @@
         <v/>
       </c>
       <c r="L771" s="26" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="772" spans="1:12" x14ac:dyDescent="0.3">
@@ -30473,7 +30460,7 @@
         <v/>
       </c>
       <c r="L777" s="26" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="778" spans="1:12" x14ac:dyDescent="0.3">
@@ -30557,7 +30544,7 @@
         <v>428</v>
       </c>
       <c r="E780" s="21" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="F780" s="22" t="str">
         <f>IF(OR(E780="",E780="!!!"),"",IF(NOT(ISNA(VLOOKUP(E780,E$1:E779,1,FALSE()))),"OLD",IF(AND(E780&lt;&gt;"",E780&lt;&gt;"!!!"),"NEW","")))</f>
@@ -31139,7 +31126,7 @@
         <v>52</v>
       </c>
       <c r="E796" s="21" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="F796" s="22" t="str">
         <f>IF(OR(E796="",E796="!!!"),"",IF(NOT(ISNA(VLOOKUP(E796,E$1:E795,1,FALSE()))),"OLD",IF(AND(E796&lt;&gt;"",E796&lt;&gt;"!!!"),"NEW","")))</f>
@@ -31348,7 +31335,7 @@
         <v>130</v>
       </c>
       <c r="E802" s="21" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="F802" s="22" t="str">
         <f>IF(OR(E802="",E802="!!!"),"",IF(NOT(ISNA(VLOOKUP(E802,E$1:E801,1,FALSE()))),"OLD",IF(AND(E802&lt;&gt;"",E802&lt;&gt;"!!!"),"NEW","")))</f>
@@ -31683,7 +31670,7 @@
         <v>52</v>
       </c>
       <c r="E811" s="21" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="F811" s="22" t="str">
         <f>IF(OR(E811="",E811="!!!"),"",IF(NOT(ISNA(VLOOKUP(E811,E$1:E810,1,FALSE()))),"OLD",IF(AND(E811&lt;&gt;"",E811&lt;&gt;"!!!"),"NEW","")))</f>
@@ -32149,7 +32136,7 @@
         <v>52</v>
       </c>
       <c r="E824" s="21" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="F824" s="22" t="str">
         <f>IF(OR(E824="",E824="!!!"),"",IF(NOT(ISNA(VLOOKUP(E824,E$1:E823,1,FALSE()))),"OLD",IF(AND(E824&lt;&gt;"",E824&lt;&gt;"!!!"),"NEW","")))</f>
@@ -32332,7 +32319,7 @@
         <v>445</v>
       </c>
       <c r="E829" s="21" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="F829" s="22" t="str">
         <f>IF(OR(E829="",E829="!!!"),"",IF(NOT(ISNA(VLOOKUP(E829,E$1:E828,1,FALSE()))),"OLD",IF(AND(E829&lt;&gt;"",E829&lt;&gt;"!!!"),"NEW","")))</f>
@@ -32359,7 +32346,7 @@
         <v>0</v>
       </c>
       <c r="L829" s="26" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="830" spans="1:12" x14ac:dyDescent="0.3">
@@ -32829,7 +32816,7 @@
         <v>88</v>
       </c>
       <c r="E843" s="21" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F843" s="22" t="s">
         <v>509</v>
@@ -32979,7 +32966,7 @@
         <v>455</v>
       </c>
       <c r="E847" s="21" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F847" s="22" t="str">
         <f>IF(OR(E847="",E847="!!!"),"",IF(NOT(ISNA(VLOOKUP(E847,E$1:E846,1,FALSE()))),"OLD",IF(AND(E847&lt;&gt;"",E847&lt;&gt;"!!!"),"NEW","")))</f>
@@ -33018,7 +33005,7 @@
         <v>458</v>
       </c>
       <c r="E848" s="21" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="F848" s="22" t="str">
         <f>IF(OR(E848="",E848="!!!"),"",IF(NOT(ISNA(VLOOKUP(E848,E$1:E847,1,FALSE()))),"OLD",IF(AND(E848&lt;&gt;"",E848&lt;&gt;"!!!"),"NEW","")))</f>
@@ -33386,7 +33373,7 @@
         <v>52</v>
       </c>
       <c r="E858" s="21" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="F858" s="22" t="str">
         <f>IF(OR(E858="",E858="!!!"),"",IF(NOT(ISNA(VLOOKUP(E858,E$1:E857,1,FALSE()))),"OLD",IF(AND(E858&lt;&gt;"",E858&lt;&gt;"!!!"),"NEW","")))</f>
@@ -33956,7 +33943,7 @@
         <v>58</v>
       </c>
       <c r="E874" s="21" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F874" s="22" t="str">
         <f>IF(OR(E874="",E874="!!!"),"",IF(NOT(ISNA(VLOOKUP(E874,E$1:E873,1,FALSE()))),"OLD",IF(AND(E874&lt;&gt;"",E874&lt;&gt;"!!!"),"NEW","")))</f>
@@ -34468,7 +34455,7 @@
         <v>52</v>
       </c>
       <c r="E888" s="21" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="F888" s="22" t="str">
         <f>IF(OR(E888="",E888="!!!"),"",IF(NOT(ISNA(VLOOKUP(E888,E$1:E887,1,FALSE()))),"OLD",IF(AND(E888&lt;&gt;"",E888&lt;&gt;"!!!"),"NEW","")))</f>
@@ -34747,7 +34734,7 @@
         <v>76</v>
       </c>
       <c r="E896" s="21" t="str">
-        <f t="shared" ref="E896:E959" si="34">IF(D896="?OLD","!!!","")</f>
+        <f t="shared" ref="E896:E912" si="34">IF(D896="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F896" s="22" t="str">
@@ -34759,7 +34746,7 @@
         <v/>
       </c>
       <c r="H896" s="24" t="str">
-        <f t="shared" ref="H896:H959" ca="1" si="35">IF(J896&lt;&gt;1,"",IF(I896="SBJ","CB","?"))</f>
+        <f t="shared" ref="H896:H912" ca="1" si="35">IF(J896&lt;&gt;1,"",IF(I896="SBJ","CB","?"))</f>
         <v/>
       </c>
       <c r="I896" s="25" t="str">
@@ -34892,7 +34879,7 @@
         <v>52</v>
       </c>
       <c r="E900" s="21" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="F900" s="22" t="str">
         <f>IF(OR(E900="",E900="!!!"),"",IF(NOT(ISNA(VLOOKUP(E900,E$1:E899,1,FALSE()))),"OLD",IF(AND(E900&lt;&gt;"",E900&lt;&gt;"!!!"),"NEW","")))</f>
@@ -35230,7 +35217,7 @@
         <v>52</v>
       </c>
       <c r="E909" s="21" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="F909" s="22" t="str">
         <f>IF(OR(E909="",E909="!!!"),"",IF(NOT(ISNA(VLOOKUP(E909,E$1:E908,1,FALSE()))),"OLD",IF(AND(E909&lt;&gt;"",E909&lt;&gt;"!!!"),"NEW","")))</f>
@@ -35773,7 +35760,7 @@
         <v>52</v>
       </c>
       <c r="E926" s="21" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F926" s="22" t="str">
         <f>IF(OR(E926="",E926="!!!"),"",IF(NOT(ISNA(VLOOKUP(E926,E$1:E925,1,FALSE()))),"OLD",IF(AND(E926&lt;&gt;"",E926&lt;&gt;"!!!"),"NEW","")))</f>
@@ -36072,7 +36059,7 @@
         <v>52</v>
       </c>
       <c r="E934" s="21" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F934" s="22" t="str">
         <f>IF(OR(E934="",E934="!!!"),"",IF(NOT(ISNA(VLOOKUP(E934,E$1:E933,1,FALSE()))),"OLD",IF(AND(E934&lt;&gt;"",E934&lt;&gt;"!!!"),"NEW","")))</f>
@@ -36541,7 +36528,7 @@
         <v>489</v>
       </c>
       <c r="E947" s="21" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="F947" s="22" t="str">
         <f>IF(OR(E947="",E947="!!!"),"",IF(NOT(ISNA(VLOOKUP(E947,E$1:E946,1,FALSE()))),"OLD",IF(AND(E947&lt;&gt;"",E947&lt;&gt;"!!!"),"NEW","")))</f>
@@ -36568,7 +36555,7 @@
         <v/>
       </c>
       <c r="L947" s="26" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="948" spans="1:12" x14ac:dyDescent="0.3">
@@ -36576,7 +36563,7 @@
         <v>103</v>
       </c>
       <c r="E948" s="21" t="str">
-        <f t="shared" ref="E947:E978" si="39">IF(D948="?OLD","!!!","")</f>
+        <f t="shared" ref="E948:E978" si="39">IF(D948="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F948" s="22" t="str">
@@ -36847,7 +36834,7 @@
         <v>52</v>
       </c>
       <c r="E955" s="21" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F955" s="22" t="str">
         <f>IF(OR(E955="",E955="!!!"),"",IF(NOT(ISNA(VLOOKUP(E955,E$1:E954,1,FALSE()))),"OLD",IF(AND(E955&lt;&gt;"",E955&lt;&gt;"!!!"),"NEW","")))</f>
@@ -37101,7 +37088,7 @@
         <v>52</v>
       </c>
       <c r="E962" s="21" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F962" s="22" t="str">
         <f>IF(OR(E962="",E962="!!!"),"",IF(NOT(ISNA(VLOOKUP(E962,E$1:E961,1,FALSE()))),"OLD",IF(AND(E962&lt;&gt;"",E962&lt;&gt;"!!!"),"NEW","")))</f>
@@ -37143,7 +37130,7 @@
         <v>52</v>
       </c>
       <c r="E963" s="21" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="F963" s="22" t="str">
         <f>IF(OR(E963="",E963="!!!"),"",IF(NOT(ISNA(VLOOKUP(E963,E$1:E962,1,FALSE()))),"OLD",IF(AND(E963&lt;&gt;"",E963&lt;&gt;"!!!"),"NEW","")))</f>
@@ -37287,10 +37274,10 @@
         <v>52</v>
       </c>
       <c r="E967" s="21" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F967" s="22" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G967" s="23" t="e">
         <f ca="1">IF(OR(E967="",E967="!!!"),"",IF(OR(J967=0,AND(J967=1,K967=1),AND(J967=1,I967="SBJ"),AND(J967=1,I967=0)),"?IN_FOCUS",IF(J967&lt;=2,"?ACTIVATED",IF(J967&lt;&gt;"","?FAMILIAR",IF(F967="NEW",IF(ISNA(VLOOKUP(E967,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -37313,7 +37300,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="L967" s="26" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="968" spans="1:12" x14ac:dyDescent="0.3">
@@ -37743,7 +37730,7 @@
         <v>76</v>
       </c>
       <c r="E980" s="21" t="str">
-        <f t="shared" ref="E979:E1010" si="41">IF(D980="?OLD","!!!","")</f>
+        <f t="shared" ref="E980:E1010" si="41">IF(D980="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F980" s="22" t="str">
@@ -38327,7 +38314,7 @@
         <v>52</v>
       </c>
       <c r="E996" s="21" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F996" s="22" t="s">
         <v>523</v>
@@ -38353,7 +38340,7 @@
         <v>0</v>
       </c>
       <c r="L996" s="26" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="997" spans="1:12" x14ac:dyDescent="0.3">
@@ -38404,7 +38391,7 @@
         <v>52</v>
       </c>
       <c r="E998" s="21" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F998" s="22" t="str">
         <f>IF(OR(E998="",E998="!!!"),"",IF(NOT(ISNA(VLOOKUP(E998,E$1:E997,1,FALSE()))),"OLD",IF(AND(E998&lt;&gt;"",E998&lt;&gt;"!!!"),"NEW","")))</f>
@@ -38480,7 +38467,7 @@
         <v>52</v>
       </c>
       <c r="E1000" s="21" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F1000" s="22" t="s">
         <v>516</v>
@@ -38862,7 +38849,7 @@
         <v>70</v>
       </c>
       <c r="E1011" s="21" t="str">
-        <f t="shared" ref="E1011:E1042" si="42">IF(D1011="?OLD","!!!","")</f>
+        <f t="shared" ref="E1011:E1033" si="42">IF(D1011="?OLD","!!!","")</f>
         <v/>
       </c>
       <c r="F1011" s="22" t="str">
@@ -38874,7 +38861,7 @@
         <v/>
       </c>
       <c r="H1011" s="24" t="str">
-        <f t="shared" ref="H1011:H1042" ca="1" si="43">IF(J1011&lt;&gt;1,"",IF(I1011="SBJ","CB","?"))</f>
+        <f t="shared" ref="H1011:H1033" ca="1" si="43">IF(J1011&lt;&gt;1,"",IF(I1011="SBJ","CB","?"))</f>
         <v/>
       </c>
       <c r="I1011" s="25" t="str">
@@ -38905,7 +38892,7 @@
         <v>52</v>
       </c>
       <c r="E1012" s="21" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F1012" s="22" t="str">
         <f>IF(OR(E1012="",E1012="!!!"),"",IF(NOT(ISNA(VLOOKUP(E1012,E$1:E1011,1,FALSE()))),"OLD",IF(AND(E1012&lt;&gt;"",E1012&lt;&gt;"!!!"),"NEW","")))</f>
